--- a/resources/views/template-invoice/invoice_sistem.xlsx
+++ b/resources/views/template-invoice/invoice_sistem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT\reguler\resources\views\template-invoice\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafie Pradipta\Documents\Works\LSP Gatensi Karya Konstruksi\Smart Gatensi\gatensi-backend\resources\views\template-invoice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72A661F-EB12-458F-98F9-536B9C330191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3AC51A5-CC78-4C76-99AD-033D1CB78812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="931" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="931" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="46" r:id="rId1"/>
@@ -35,11 +35,24 @@
     <definedName name="TERBILANG">[3]Terbilang!$D$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>Ditagihkan Kepada:</t>
   </si>
@@ -135,6 +148,15 @@
   </si>
   <si>
     <t>Kategori bla bla</t>
+  </si>
+  <si>
+    <t>LSP GATENSI KARYA KONSTRUKSI</t>
+  </si>
+  <si>
+    <t>SILVIANA ROSMA DP</t>
+  </si>
+  <si>
+    <t>FINANCE</t>
   </si>
 </sst>
 </file>
@@ -215,13 +237,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Berlin Sans FB Demi"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -251,6 +266,13 @@
       <sz val="52"/>
       <color theme="1"/>
       <name val="Berlin Sans FB Demi"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Berlin Sans FB"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -362,11 +384,11 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -394,9 +416,6 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -427,7 +446,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -463,7 +482,7 @@
     <xf numFmtId="165" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -475,20 +494,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -601,11 +623,87 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>518432</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>174171</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1066800" cy="2000250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="image2.png" descr="729aeff7-08e0-4889-b6af-00c062dca145-removebg-preview">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF3C3AAA-AF3C-4F68-88B5-199D875F8E11}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11981089" y="6901542"/>
+          <a:ext cx="1066800" cy="2000250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1186543</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>114633</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1524000" cy="1485900"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="image3.png" descr="cap">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D45E9EC3-2B25-4403-947D-09CFCCF99551}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10961914" y="7342747"/>
+          <a:ext cx="1524000" cy="1485900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet2"/>
@@ -644,7 +742,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="MENU"/>
@@ -683,7 +781,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet2"/>
@@ -724,7 +822,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet2"/>
@@ -769,7 +867,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="dftr peg"/>
@@ -814,7 +912,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="FORM SPPD"/>
@@ -1372,26 +1470,26 @@
   <sheetData>
     <row r="3" spans="2:10" ht="17.399999999999999" customHeight="1"/>
     <row r="4" spans="2:10">
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="38"/>
+      <c r="D4" s="36"/>
     </row>
     <row r="5" spans="2:10" ht="22.2" customHeight="1">
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
     </row>
     <row r="6" spans="2:10" ht="22.2" customHeight="1">
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
     </row>
     <row r="7" spans="2:10">
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
     </row>
     <row r="8" spans="2:10" ht="18">
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
     </row>
     <row r="10" spans="2:10" ht="20.399999999999999">
       <c r="B10" s="6" t="s">
@@ -1406,10 +1504,10 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="20.399999999999999">
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="40"/>
+      <c r="C11" s="38"/>
       <c r="F11" s="7" t="s">
         <v>3</v>
       </c>
@@ -1418,12 +1516,12 @@
       </c>
     </row>
     <row r="12" spans="2:10" ht="20.399999999999999">
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="40"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
+      <c r="C12" s="38"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="9"/>
     </row>
     <row r="13" spans="2:10" ht="20.399999999999999">
       <c r="B13" s="6"/>
@@ -1433,111 +1531,111 @@
       <c r="B14" s="4"/>
     </row>
     <row r="15" spans="2:10" ht="18" customHeight="1">
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="18" customHeight="1">
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <v>45115</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="18" customHeight="1">
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="18" customHeight="1">
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="12" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="18" customHeight="1">
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="33" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="49.95" customHeight="1">
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="39"/>
-      <c r="E21" s="14" t="s">
+      <c r="D21" s="37"/>
+      <c r="E21" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="22" spans="2:7" s="2" customFormat="1" ht="19.95" customHeight="1">
-      <c r="B22" s="16">
+      <c r="B22" s="15">
         <v>1</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="19" t="s">
+      <c r="D22" s="17"/>
+      <c r="E22" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="19">
         <v>4</v>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="20">
         <v>50000</v>
       </c>
     </row>
     <row r="23" spans="2:7" s="3" customFormat="1" ht="10.050000000000001" customHeight="1">
-      <c r="B23" s="22"/>
+      <c r="B23" s="21"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="25"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="24"/>
     </row>
     <row r="24" spans="2:7" s="3" customFormat="1" ht="19.95" customHeight="1">
       <c r="B24" s="5"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="26"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="25"/>
     </row>
     <row r="25" spans="2:7" s="3" customFormat="1" ht="19.95" customHeight="1">
       <c r="B25" s="5"/>
@@ -1545,63 +1643,63 @@
         <v>18</v>
       </c>
       <c r="D25" s="4"/>
-      <c r="E25" s="33" t="str">
+      <c r="E25" s="32" t="str">
         <f>"# "&amp;PROPER(IF(G27=0,"nol",IF(G27&lt;0,"minus ","")&amp;SUBSTITUTE(TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(IF(--MID(TEXT(ABS(G27),"000000000000000"),1,3)=0,"",MID(TEXT(ABS(G27),"000000000000000"),1,1)&amp;" ratus "&amp;MID(TEXT(ABS(G27),"000000000000000"),2,1)&amp;" puluh "&amp;MID(TEXT(ABS(G27),"000000000000000"),3,1)&amp;" trilyun ")&amp;IF(--MID(TEXT(ABS(G27),"000000000000000"),4,3)=0,"",MID(TEXT(ABS(G27),"000000000000000"),4,1)&amp;" ratus "&amp;MID(TEXT(ABS(G27),"000000000000000"),5,1)&amp;" puluh "&amp;MID(TEXT(ABS(G27),"000000000000000"),6,1)&amp;" milyar ")&amp;IF(--MID(TEXT(ABS(G27),"000000000000000"),7,3)=0,"",MID(TEXT(ABS(G27),"000000000000000"),7,1)&amp;" ratus "&amp;MID(TEXT(ABS(G27),"000000000000000"),8,1)&amp;" puluh "&amp;MID(TEXT(ABS(G27),"000000000000000"),9,1)&amp;" juta ")&amp;IF(--MID(TEXT(ABS(G27),"000000000000000"),10,3)=0,"",IF(--MID(TEXT(ABS(G27),"000000000000000"),10,3)=1,"*",MID(TEXT(ABS(G27),"000000000000000"),10,1)&amp;" ratus "&amp;MID(TEXT(ABS(G27),"000000000000000"),11,1)&amp;" puluh ")&amp;MID(TEXT(ABS(G27),"000000000000000"),12,1)&amp;" ribu ")&amp;IF(--MID(TEXT(ABS(G27),"000000000000000"),13,3)=0,"",MID(TEXT(ABS(G27),"000000000000000"),13,1)&amp;" ratus "&amp;MID(TEXT(ABS(G27),"000000000000000"),14,1)&amp;" puluh "&amp;MID(TEXT(ABS(G27),"000000000000000"),15,1)),1,"satu"),2,"dua"),3,"tiga"),4,"empat"),5,"lima"),6,"enam"),7,"tujuh"),8,"delapan"),9,"sembilan"),"0 ratus",""),"0 puluh",""),"satu puluh 0","sepuluh"),"satu puluh satu","sebelas"),"satu puluh dua","duabelas"),"satu puluh tiga","tigabelas"),"satu puluh empat","empatbelas"),"satu puluh lima","limabelas"),"satu puluh enam","enambelas"),"satu puluh tujuh","tujuhbelas"),"satu puluh delapan","delapanbelas"),"satu puluh sembilan","sembilanbelas"),"satu ratus","seratus"),"*satu ribu","seribu"),0,"")),"  "," "))&amp;" Rupiah")&amp;" #"</f>
         <v># Lima Puluh Ribu Rupiah #</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="26">
         <f>SUM(G22)</f>
         <v>50000</v>
       </c>
     </row>
     <row r="26" spans="2:7" s="3" customFormat="1" ht="19.95" customHeight="1">
       <c r="B26" s="5"/>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="11"/>
+      <c r="D26" s="10"/>
       <c r="E26" s="4"/>
       <c r="F26" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G26" s="29">
+      <c r="G26" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:7" s="3" customFormat="1" ht="19.95" customHeight="1">
       <c r="B27" s="5"/>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="11"/>
+      <c r="D27" s="10"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="30" t="s">
+      <c r="F27" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="30">
         <f>G25-G26</f>
         <v>50000</v>
       </c>
     </row>
     <row r="28" spans="2:7" s="3" customFormat="1" ht="19.95" customHeight="1">
       <c r="B28" s="5"/>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="11"/>
+      <c r="D28" s="10"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
     </row>
     <row r="29" spans="2:7" s="3" customFormat="1" ht="19.95" customHeight="1">
       <c r="B29" s="5"/>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="11"/>
+      <c r="D29" s="10"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -1611,19 +1709,22 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+      <c r="F30" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="39"/>
     </row>
     <row r="31" spans="2:7" s="3" customFormat="1" ht="19.95" customHeight="1">
       <c r="B31" s="5"/>
-      <c r="C31" s="4"/>
+      <c r="C31" s="27"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
     </row>
     <row r="32" spans="2:7" s="3" customFormat="1" ht="19.95" customHeight="1">
       <c r="B32" s="5"/>
-      <c r="C32" s="4"/>
+      <c r="C32" s="27"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
@@ -1633,7 +1734,6 @@
       <c r="B33" s="5"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="6"/>
     </row>
@@ -1658,24 +1758,28 @@
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="6"/>
+      <c r="F36" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" s="40"/>
     </row>
     <row r="37" spans="2:7" s="3" customFormat="1" ht="19.95" customHeight="1">
       <c r="B37" s="5"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
+      <c r="F37" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="G37" s="39"/>
     </row>
     <row r="38" spans="2:7" s="3" customFormat="1" ht="19.95" customHeight="1">
       <c r="B38" s="5"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="35"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
     </row>
     <row r="39" spans="2:7" s="3" customFormat="1" ht="19.95" customHeight="1">
       <c r="B39" s="5"/>
@@ -1794,7 +1898,7 @@
     <sortCondition ref="C23:C53"/>
     <sortCondition ref="E23:E53"/>
   </sortState>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="F38:G38"/>
@@ -1803,10 +1907,12 @@
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F36:G36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39305555555555599" right="0.39305555555555599" top="0.59027777777777801" bottom="0.39305555555555599" header="0.31458333333333299" footer="0.31458333333333299"/>
-  <pageSetup paperSize="9" scale="46" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter scaleWithDoc="0"/>
   <drawing r:id="rId2"/>
 </worksheet>
